--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.3996,0.1723,0.0546,0.4643</t>
-  </si>
-  <si>
-    <t>0.0289,0.0247,0.0247,0.9719</t>
-  </si>
-  <si>
-    <t>0.6033,0.0967,0.0918,0.2197</t>
-  </si>
-  <si>
-    <t>0.0542,0.0322,0.0247,0.9563</t>
-  </si>
-  <si>
-    <t>0.9854,0.0181,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9658,0.0343,0.0035,0.0027</t>
-  </si>
-  <si>
-    <t>0.9578,0.0274,0.0136,0.0035</t>
-  </si>
-  <si>
-    <t>0.9742,0.0190,0.0069,0.0017</t>
-  </si>
-  <si>
-    <t>0.9652,0.0285,0.0068,0.0035</t>
-  </si>
-  <si>
-    <t>0.9807,0.0190,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9861,0.0106,0.0011,0.0017</t>
-  </si>
-  <si>
-    <t>0.9738,0.0196,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.2519,0.1552,0.6189,0.0172</t>
-  </si>
-  <si>
-    <t>0.1133,0.0812,0.8215,0.0113</t>
-  </si>
-  <si>
-    <t>0.2671,0.0862,0.7016,0.0223</t>
-  </si>
-  <si>
-    <t>0.0492,0.0696,0.9123,0.0082</t>
-  </si>
-  <si>
-    <t>0.3368,0.0810,0.6471,0.0344</t>
-  </si>
-  <si>
-    <t>0.2094,0.8093,0.0484,0.0113</t>
-  </si>
-  <si>
-    <t>0.0836,0.9069,0.0541,0.0038</t>
-  </si>
-  <si>
-    <t>0.7384,0.2779,0.0366,0.0092</t>
-  </si>
-  <si>
-    <t>0.1237,0.8885,0.0324,0.0053</t>
-  </si>
-  <si>
-    <t>0.0571,0.9330,0.0463,0.0026</t>
-  </si>
-  <si>
-    <t>0.1653,0.0458,0.8082,0.0231</t>
-  </si>
-  <si>
-    <t>0.1583,0.1071,0.6815,0.1534</t>
-  </si>
-  <si>
-    <t>0.0127,0.0050,0.9826,0.0061</t>
-  </si>
-  <si>
-    <t>0.1654,0.0466,0.7989,0.0340</t>
-  </si>
-  <si>
-    <t>0.1109,0.0239,0.8888,0.0109</t>
-  </si>
-  <si>
-    <t>0.0794,0.0134,0.9189,0.0203</t>
-  </si>
-  <si>
-    <t>0.0069,0.0038,0.9827,0.0123</t>
-  </si>
-  <si>
-    <t>0.3822,0.5902,0.0988,0.0185</t>
-  </si>
-  <si>
-    <t>0.3652,0.0656,0.6708,0.0194</t>
-  </si>
-  <si>
-    <t>0.0006,0.0077,0.9970,0.0012</t>
-  </si>
-  <si>
-    <t>0.1054,0.2327,0.7319,0.0081</t>
-  </si>
-  <si>
-    <t>0.5289,0.3951,0.1397,0.0306</t>
-  </si>
-  <si>
-    <t>0.6353,0.2213,0.2030,0.0261</t>
-  </si>
-  <si>
-    <t>0.4449,0.5577,0.1052,0.0066</t>
-  </si>
-  <si>
-    <t>0.1860,0.6964,0.1939,0.0157</t>
-  </si>
-  <si>
-    <t>0.0123,0.1728,0.9292,0.0111</t>
-  </si>
-  <si>
-    <t>0.0450,0.0347,0.9179,0.0338</t>
-  </si>
-  <si>
-    <t>0.0280,0.2536,0.8774,0.0227</t>
-  </si>
-  <si>
-    <t>0.0441,0.0129,0.9332,0.0293</t>
-  </si>
-  <si>
-    <t>0.0537,0.1702,0.8435,0.0157</t>
-  </si>
-  <si>
-    <t>0.0207,0.7735,0.6334,0.0096</t>
-  </si>
-  <si>
-    <t>0.0306,0.0801,0.9167,0.0231</t>
-  </si>
-  <si>
-    <t>0.1425,0.6533,0.2896,0.1342</t>
-  </si>
-  <si>
-    <t>0.0174,0.9493,0.1148,0.0034</t>
-  </si>
-  <si>
-    <t>0.0365,0.6123,0.6866,0.0145</t>
-  </si>
-  <si>
-    <t>0.0093,0.9357,0.1089,0.0102</t>
-  </si>
-  <si>
-    <t>0.0025,0.0201,0.9795,0.0192</t>
-  </si>
-  <si>
-    <t>0.0014,0.0154,0.9939,0.0014</t>
-  </si>
-  <si>
-    <t>0.0493,0.0130,0.9325,0.0263</t>
-  </si>
-  <si>
-    <t>0.0540,0.0299,0.9218,0.0087</t>
-  </si>
-  <si>
-    <t>0.0120,0.0187,0.9625,0.0208</t>
-  </si>
-  <si>
-    <t>0.0051,0.0943,0.9742,0.0031</t>
-  </si>
-  <si>
-    <t>0.9006,0.1318,0.0099,0.0030</t>
-  </si>
-  <si>
-    <t>0.9319,0.0659,0.0162,0.0041</t>
-  </si>
-  <si>
-    <t>0.9690,0.0275,0.0039,0.0030</t>
-  </si>
-  <si>
-    <t>0.0255,0.0308,0.9642,0.0119</t>
-  </si>
-  <si>
-    <t>0.9422,0.0503,0.0195,0.0037</t>
-  </si>
-  <si>
-    <t>0.9420,0.0721,0.0086,0.0028</t>
-  </si>
-  <si>
-    <t>0.9577,0.0421,0.0068,0.0025</t>
-  </si>
-  <si>
-    <t>0.0021,0.1955,0.9791,0.0016</t>
-  </si>
-  <si>
-    <t>0.0038,0.0276,0.9851,0.0075</t>
-  </si>
-  <si>
-    <t>0.0054,0.0261,0.9811,0.0044</t>
-  </si>
-  <si>
-    <t>0.0023,0.5696,0.9443,0.0021</t>
-  </si>
-  <si>
-    <t>0.0061,0.0157,0.9849,0.0042</t>
-  </si>
-  <si>
-    <t>0.0420,0.9056,0.1913,0.0064</t>
-  </si>
-  <si>
-    <t>0.0074,0.9828,0.0468,0.0008</t>
-  </si>
-  <si>
-    <t>0.6861,0.0514,0.3416,0.0199</t>
-  </si>
-  <si>
-    <t>0.4504,0.2684,0.3173,0.0200</t>
-  </si>
-  <si>
-    <t>0.0136,0.0256,0.9770,0.0040</t>
-  </si>
-  <si>
-    <t>0.0052,0.3664,0.9425,0.0033</t>
-  </si>
-  <si>
-    <t>0.0090,0.6597,0.8501,0.0065</t>
-  </si>
-  <si>
-    <t>0.0019,0.9485,0.6613,0.0011</t>
-  </si>
-  <si>
-    <t>0.0031,0.6086,0.9209,0.0024</t>
-  </si>
-  <si>
-    <t>0.0083,0.0089,0.0217,0.9875</t>
-  </si>
-  <si>
-    <t>0.0066,0.0116,0.0060,0.9935</t>
-  </si>
-  <si>
-    <t>0.0028,0.0089,0.0071,0.9959</t>
-  </si>
-  <si>
-    <t>0.0372,0.0230,0.0447,0.9553</t>
-  </si>
-  <si>
-    <t>0.0328,0.0205,0.0754,0.9477</t>
-  </si>
-  <si>
-    <t>0.0022,0.0089,0.0040,0.9972</t>
-  </si>
-  <si>
-    <t>0.0093,0.7849,0.7548,0.0046</t>
-  </si>
-  <si>
-    <t>0.0030,0.2355,0.9715,0.0018</t>
-  </si>
-  <si>
-    <t>0.0022,0.4747,0.9492,0.0022</t>
-  </si>
-  <si>
-    <t>0.0108,0.3915,0.9117,0.0084</t>
-  </si>
-  <si>
-    <t>0.0049,0.6655,0.8873,0.0028</t>
-  </si>
-  <si>
-    <t>0.0135,0.2456,0.9167,0.0049</t>
-  </si>
-  <si>
-    <t>0.9751,0.0297,0.0036,0.0013</t>
-  </si>
-  <si>
-    <t>0.9611,0.0428,0.0058,0.0019</t>
-  </si>
-  <si>
-    <t>0.9721,0.0317,0.0025,0.0013</t>
-  </si>
-  <si>
-    <t>0.9775,0.0158,0.0021,0.0029</t>
-  </si>
-  <si>
-    <t>0.9612,0.0444,0.0037,0.0024</t>
-  </si>
-  <si>
-    <t>0.9730,0.0234,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.9697,0.0255,0.0044,0.0025</t>
-  </si>
-  <si>
-    <t>0.9445,0.0603,0.0073,0.0038</t>
-  </si>
-  <si>
-    <t>0.9808,0.0111,0.0016,0.0033</t>
-  </si>
-  <si>
-    <t>0.9799,0.0224,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9831,0.0132,0.0017,0.0018</t>
-  </si>
-  <si>
-    <t>0.9765,0.0200,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9826,0.0148,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9700,0.0251,0.0065,0.0024</t>
-  </si>
-  <si>
-    <t>0.9755,0.0193,0.0026,0.0025</t>
-  </si>
-  <si>
-    <t>0.9799,0.0194,0.0026,0.0014</t>
-  </si>
-  <si>
-    <t>0.0032,0.0046,0.9895,0.0060</t>
-  </si>
-  <si>
-    <t>0.1165,0.1344,0.7604,0.0154</t>
-  </si>
-  <si>
-    <t>0.1723,0.1210,0.1503,0.7567</t>
-  </si>
-  <si>
-    <t>0.0540,0.0149,0.9388,0.0079</t>
-  </si>
-  <si>
-    <t>0.2372,0.7900,0.0659,0.0070</t>
-  </si>
-  <si>
-    <t>0.0512,0.9323,0.0627,0.0024</t>
-  </si>
-  <si>
-    <t>0.0900,0.9171,0.0166,0.0036</t>
-  </si>
-  <si>
-    <t>0.2619,0.7370,0.0725,0.0173</t>
-  </si>
-  <si>
-    <t>0.1910,0.8135,0.0756,0.0097</t>
-  </si>
-  <si>
-    <t>0.0420,0.9487,0.0400,0.0013</t>
-  </si>
-  <si>
-    <t>0.8295,0.2499,0.0106,0.0036</t>
-  </si>
-  <si>
-    <t>0.1142,0.3530,0.6083,0.0101</t>
-  </si>
-  <si>
-    <t>0.0715,0.0153,0.9307,0.0080</t>
-  </si>
-  <si>
-    <t>0.2905,0.0700,0.6916,0.0357</t>
-  </si>
-  <si>
-    <t>0.2229,0.0233,0.8213,0.0207</t>
-  </si>
-  <si>
-    <t>0.4529,0.1130,0.4247,0.1795</t>
-  </si>
-  <si>
-    <t>0.0177,0.9494,0.1052,0.0028</t>
-  </si>
-  <si>
-    <t>0.0366,0.9046,0.1577,0.0082</t>
-  </si>
-  <si>
-    <t>0.2012,0.5180,0.3560,0.0568</t>
-  </si>
-  <si>
-    <t>0.0023,0.9166,0.7527,0.0010</t>
-  </si>
-  <si>
-    <t>0.0911,0.8089,0.2359,0.0121</t>
-  </si>
-  <si>
-    <t>0.5305,0.5525,0.0410,0.0064</t>
-  </si>
-  <si>
-    <t>0.5552,0.5151,0.0463,0.0062</t>
-  </si>
-  <si>
-    <t>0.9472,0.0462,0.0088,0.0044</t>
-  </si>
-  <si>
-    <t>0.9298,0.0576,0.0078,0.0088</t>
-  </si>
-  <si>
-    <t>0.9513,0.0285,0.0105,0.0105</t>
-  </si>
-  <si>
-    <t>0.9507,0.0393,0.0059,0.0050</t>
-  </si>
-  <si>
-    <t>0.9749,0.0187,0.0019,0.0028</t>
-  </si>
-  <si>
-    <t>0.8396,0.0585,0.1096,0.0160</t>
-  </si>
-  <si>
-    <t>0.9639,0.0181,0.0126,0.0040</t>
-  </si>
-  <si>
-    <t>0.9600,0.0214,0.0105,0.0068</t>
-  </si>
-  <si>
-    <t>0.0045,0.2249,0.9625,0.0020</t>
-  </si>
-  <si>
-    <t>0.0024,0.6528,0.9311,0.0014</t>
-  </si>
-  <si>
-    <t>0.0142,0.3274,0.9052,0.0062</t>
-  </si>
-  <si>
-    <t>0.0359,0.1050,0.8978,0.0119</t>
-  </si>
-  <si>
-    <t>0.4039,0.0958,0.5400,0.1568</t>
-  </si>
-  <si>
-    <t>0.4471,0.0609,0.5914,0.0298</t>
-  </si>
-  <si>
-    <t>0.2933,0.0307,0.7593,0.0162</t>
-  </si>
-  <si>
-    <t>0.3230,0.1830,0.5203,0.0228</t>
-  </si>
-  <si>
-    <t>0.0386,0.0212,0.0233,0.9673</t>
-  </si>
-  <si>
-    <t>0.0011,0.0036,0.0026,0.9985</t>
-  </si>
-  <si>
-    <t>0.0036,0.0087,0.0050,0.9956</t>
-  </si>
-  <si>
-    <t>0.0073,0.0070,0.0083,0.9928</t>
-  </si>
-  <si>
-    <t>0.0022,0.6056,0.9303,0.0020</t>
-  </si>
-  <si>
-    <t>0.9351,0.0566,0.0061,0.0078</t>
-  </si>
-  <si>
-    <t>0.8459,0.1956,0.0184,0.0057</t>
-  </si>
-  <si>
-    <t>0.9391,0.0412,0.0062,0.0113</t>
-  </si>
-  <si>
-    <t>0.7622,0.2970,0.0269,0.0061</t>
-  </si>
-  <si>
-    <t>0.9080,0.0475,0.0270,0.0222</t>
-  </si>
-  <si>
-    <t>0.5203,0.0392,0.1287,0.3211</t>
-  </si>
-  <si>
-    <t>0.9131,0.0543,0.0314,0.0098</t>
-  </si>
-  <si>
-    <t>0.0375,0.2223,0.8684,0.0299</t>
-  </si>
-  <si>
-    <t>0.4747,0.0110,0.1395,0.2639</t>
-  </si>
-  <si>
-    <t>0.6186,0.0555,0.2955,0.0780</t>
-  </si>
-  <si>
-    <t>0.3339,0.4248,0.2956,0.0371</t>
-  </si>
-  <si>
-    <t>0.7036,0.1485,0.1333,0.0829</t>
-  </si>
-  <si>
-    <t>0.3417,0.2358,0.4776,0.0165</t>
-  </si>
-  <si>
-    <t>0.3203,0.5767,0.1712,0.0408</t>
-  </si>
-  <si>
-    <t>0.2936,0.1507,0.6054,0.0167</t>
-  </si>
-  <si>
-    <t>0.5975,0.1492,0.3020,0.0477</t>
-  </si>
-  <si>
-    <t>0.9720,0.0182,0.0037,0.0036</t>
-  </si>
-  <si>
-    <t>0.9747,0.0158,0.0036,0.0036</t>
-  </si>
-  <si>
-    <t>0.9759,0.0238,0.0036,0.0016</t>
-  </si>
-  <si>
-    <t>0.9564,0.0364,0.0108,0.0039</t>
-  </si>
-  <si>
-    <t>0.9526,0.0310,0.0092,0.0068</t>
-  </si>
-  <si>
-    <t>0.9594,0.0361,0.0041,0.0042</t>
-  </si>
-  <si>
-    <t>0.9667,0.0224,0.0033,0.0049</t>
-  </si>
-  <si>
-    <t>0.9813,0.0141,0.0014,0.0026</t>
-  </si>
-  <si>
-    <t>0.0987,0.8981,0.0445,0.0050</t>
-  </si>
-  <si>
-    <t>0.7299,0.3481,0.0332,0.0051</t>
-  </si>
-  <si>
-    <t>0.3695,0.6971,0.0453,0.0054</t>
-  </si>
-  <si>
-    <t>0.7513,0.2185,0.1022,0.0084</t>
-  </si>
-  <si>
-    <t>0.9437,0.0616,0.0096,0.0038</t>
-  </si>
-  <si>
-    <t>0.7461,0.2875,0.0311,0.0113</t>
-  </si>
-  <si>
-    <t>0.9430,0.0605,0.0073,0.0030</t>
-  </si>
-  <si>
-    <t>0.8232,0.1158,0.0952,0.0047</t>
-  </si>
-  <si>
-    <t>0.0363,0.0238,0.9621,0.0066</t>
-  </si>
-  <si>
-    <t>0.9390,0.0536,0.0087,0.0075</t>
-  </si>
-  <si>
-    <t>0.0020,0.0050,0.9946,0.0013</t>
-  </si>
-  <si>
-    <t>0.0144,0.1510,0.9346,0.0096</t>
-  </si>
-  <si>
-    <t>0.0263,0.0323,0.9576,0.0036</t>
-  </si>
-  <si>
-    <t>0.0009,0.1786,0.9866,0.0016</t>
-  </si>
-  <si>
-    <t>0.0103,0.0090,0.9810,0.0039</t>
-  </si>
-  <si>
-    <t>0.0198,0.0055,0.9790,0.0031</t>
-  </si>
-  <si>
-    <t>0.0160,0.0203,0.9736,0.0020</t>
-  </si>
-  <si>
-    <t>0.1830,0.0257,0.8425,0.0124</t>
-  </si>
-  <si>
-    <t>0.1559,0.0446,0.8404,0.0101</t>
-  </si>
-  <si>
-    <t>0.1593,0.0629,0.8076,0.0105</t>
-  </si>
-  <si>
-    <t>0.1093,0.2679,0.6923,0.0132</t>
-  </si>
-  <si>
-    <t>0.1364,0.0667,0.8133,0.0084</t>
-  </si>
-  <si>
-    <t>0.1800,0.0260,0.8395,0.0201</t>
-  </si>
-  <si>
-    <t>0.3417,0.0741,0.6587,0.0391</t>
-  </si>
-  <si>
-    <t>0.3035,0.1098,0.6263,0.0259</t>
-  </si>
-  <si>
-    <t>0.9009,0.1492,0.0077,0.0025</t>
-  </si>
-  <si>
-    <t>0.6111,0.5319,0.0088,0.0049</t>
-  </si>
-  <si>
-    <t>0.7838,0.2629,0.0336,0.0058</t>
-  </si>
-  <si>
-    <t>0.9723,0.0216,0.0035,0.0028</t>
-  </si>
-  <si>
-    <t>0.7873,0.3016,0.0163,0.0033</t>
-  </si>
-  <si>
-    <t>0.3940,0.3092,0.3368,0.0329</t>
-  </si>
-  <si>
-    <t>0.2989,0.0437,0.7332,0.0447</t>
-  </si>
-  <si>
-    <t>0.2657,0.1298,0.2601,0.5451</t>
-  </si>
-  <si>
-    <t>0.2377,0.0303,0.7790,0.0374</t>
-  </si>
-  <si>
-    <t>0.1421,0.0191,0.8638,0.0161</t>
-  </si>
-  <si>
-    <t>0.0069,0.0082,0.9816,0.0103</t>
-  </si>
-  <si>
-    <t>0.0271,0.0507,0.9357,0.0079</t>
-  </si>
-  <si>
-    <t>0.0125,0.1640,0.9440,0.0046</t>
-  </si>
-  <si>
-    <t>0.0242,0.0299,0.9546,0.0081</t>
-  </si>
-  <si>
-    <t>0.0119,0.0104,0.9722,0.0131</t>
-  </si>
-  <si>
-    <t>0.9792,0.0163,0.0020,0.0024</t>
-  </si>
-  <si>
-    <t>0.9509,0.0618,0.0066,0.0026</t>
-  </si>
-  <si>
-    <t>0.9736,0.0186,0.0037,0.0030</t>
-  </si>
-  <si>
-    <t>0.9762,0.0259,0.0026,0.0015</t>
-  </si>
-  <si>
-    <t>0.9737,0.0230,0.0026,0.0023</t>
-  </si>
-  <si>
-    <t>0.9620,0.0371,0.0059,0.0026</t>
-  </si>
-  <si>
-    <t>0.9814,0.0166,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.9851,0.0115,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.1412,0.0327,0.8688,0.0089</t>
-  </si>
-  <si>
-    <t>0.1430,0.1227,0.7737,0.0072</t>
-  </si>
-  <si>
-    <t>0.7035,0.1917,0.1063,0.0650</t>
-  </si>
-  <si>
-    <t>0.0096,0.0441,0.9728,0.0022</t>
-  </si>
-  <si>
-    <t>0.0008,0.0040,0.9967,0.0015</t>
-  </si>
-  <si>
-    <t>0.0117,0.0105,0.9831,0.0020</t>
-  </si>
-  <si>
-    <t>0.0025,0.0040,0.9923,0.0047</t>
-  </si>
-  <si>
-    <t>0.0505,0.0174,0.9415,0.0094</t>
-  </si>
-  <si>
-    <t>0.0029,0.0274,0.9846,0.0048</t>
-  </si>
-  <si>
-    <t>0.0115,0.0431,0.9651,0.0027</t>
-  </si>
-  <si>
-    <t>0.0419,0.0405,0.9308,0.0045</t>
-  </si>
-  <si>
-    <t>0.1734,0.0293,0.8417,0.0160</t>
-  </si>
-  <si>
-    <t>0.2850,0.0135,0.6911,0.0618</t>
-  </si>
-  <si>
-    <t>0.2579,0.0655,0.7361,0.0265</t>
-  </si>
-  <si>
-    <t>0.9639,0.0293,0.0100,0.0023</t>
-  </si>
-  <si>
-    <t>0.9748,0.0265,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.9623,0.0466,0.0047,0.0018</t>
-  </si>
-  <si>
-    <t>0.9576,0.0518,0.0058,0.0022</t>
-  </si>
-  <si>
-    <t>0.9525,0.0393,0.0109,0.0040</t>
-  </si>
-  <si>
-    <t>0.9575,0.0337,0.0087,0.0032</t>
-  </si>
-  <si>
-    <t>0.9816,0.0145,0.0020,0.0017</t>
-  </si>
-  <si>
-    <t>0.9791,0.0207,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.0811,0.0509,0.8590,0.0142</t>
-  </si>
-  <si>
-    <t>0.0123,0.0459,0.9624,0.0061</t>
-  </si>
-  <si>
-    <t>0.0063,0.0232,0.9825,0.0030</t>
-  </si>
-  <si>
-    <t>0.0445,0.0393,0.9285,0.0099</t>
-  </si>
-  <si>
-    <t>0.0137,0.0098,0.9747,0.0082</t>
-  </si>
-  <si>
-    <t>0.0091,0.0076,0.9807,0.0100</t>
-  </si>
-  <si>
-    <t>0.1088,0.0503,0.8439,0.0200</t>
-  </si>
-  <si>
-    <t>0.0327,0.0233,0.9003,0.1023</t>
-  </si>
-  <si>
-    <t>0.3342,0.0258,0.0069,0.7691</t>
-  </si>
-  <si>
-    <t>0.0063,0.0292,0.0083,0.9914</t>
-  </si>
-  <si>
-    <t>0.0296,0.0178,0.0047,0.9810</t>
-  </si>
-  <si>
-    <t>0.0155,0.0138,0.0150,0.9862</t>
-  </si>
-  <si>
-    <t>0.0026,0.0074,0.0016,0.9977</t>
-  </si>
-  <si>
-    <t>0.4095,0.4645,0.2082,0.1197</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.6485,0.0881,0.0987,0.2074</t>
+  </si>
+  <si>
+    <t>0.0211,0.0166,0.0098,0.9843</t>
+  </si>
+  <si>
+    <t>0.4037,0.2402,0.0205,0.3496</t>
+  </si>
+  <si>
+    <t>0.1236,0.0249,0.0204,0.9115</t>
+  </si>
+  <si>
+    <t>0.9849,0.0105,0.0016,0.0019</t>
+  </si>
+  <si>
+    <t>0.9695,0.0317,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.9126,0.0660,0.0460,0.0047</t>
+  </si>
+  <si>
+    <t>0.9685,0.0297,0.0039,0.0024</t>
+  </si>
+  <si>
+    <t>0.9654,0.0372,0.0030,0.0027</t>
+  </si>
+  <si>
+    <t>0.9829,0.0160,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9772,0.0321,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9858,0.0103,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.1122,0.4205,0.5767,0.0248</t>
+  </si>
+  <si>
+    <t>0.1302,0.0711,0.8299,0.0107</t>
+  </si>
+  <si>
+    <t>0.2242,0.0367,0.7983,0.0132</t>
+  </si>
+  <si>
+    <t>0.1204,0.0466,0.8435,0.0097</t>
+  </si>
+  <si>
+    <t>0.3271,0.1419,0.5818,0.0362</t>
+  </si>
+  <si>
+    <t>0.1343,0.8807,0.0365,0.0071</t>
+  </si>
+  <si>
+    <t>0.1933,0.7988,0.0963,0.0109</t>
+  </si>
+  <si>
+    <t>0.3918,0.6520,0.0597,0.0069</t>
+  </si>
+  <si>
+    <t>0.1947,0.8274,0.0455,0.0080</t>
+  </si>
+  <si>
+    <t>0.0588,0.9242,0.0446,0.0036</t>
+  </si>
+  <si>
+    <t>0.1427,0.0235,0.8486,0.0474</t>
+  </si>
+  <si>
+    <t>0.2250,0.0965,0.5686,0.2439</t>
+  </si>
+  <si>
+    <t>0.0128,0.0085,0.9774,0.0060</t>
+  </si>
+  <si>
+    <t>0.2558,0.0270,0.7608,0.0302</t>
+  </si>
+  <si>
+    <t>0.0175,0.0093,0.9750,0.0043</t>
+  </si>
+  <si>
+    <t>0.1278,0.0140,0.8874,0.0270</t>
+  </si>
+  <si>
+    <t>0.0114,0.0098,0.9731,0.0155</t>
+  </si>
+  <si>
+    <t>0.5375,0.4565,0.0954,0.0194</t>
+  </si>
+  <si>
+    <t>0.2074,0.0886,0.7556,0.0107</t>
+  </si>
+  <si>
+    <t>0.0039,0.0229,0.9869,0.0051</t>
+  </si>
+  <si>
+    <t>0.1901,0.6831,0.2028,0.0176</t>
+  </si>
+  <si>
+    <t>0.5578,0.1969,0.3216,0.0419</t>
+  </si>
+  <si>
+    <t>0.6086,0.1326,0.3215,0.0239</t>
+  </si>
+  <si>
+    <t>0.5104,0.5222,0.0648,0.0081</t>
+  </si>
+  <si>
+    <t>0.1935,0.5408,0.3866,0.0400</t>
+  </si>
+  <si>
+    <t>0.0254,0.5711,0.6990,0.0355</t>
+  </si>
+  <si>
+    <t>0.0133,0.0219,0.9612,0.0227</t>
+  </si>
+  <si>
+    <t>0.0909,0.1110,0.7988,0.0959</t>
+  </si>
+  <si>
+    <t>0.0675,0.0302,0.9063,0.0186</t>
+  </si>
+  <si>
+    <t>0.0092,0.0563,0.9686,0.0053</t>
+  </si>
+  <si>
+    <t>0.0049,0.8721,0.7183,0.0031</t>
+  </si>
+  <si>
+    <t>0.0169,0.0163,0.9627,0.0198</t>
+  </si>
+  <si>
+    <t>0.5076,0.0618,0.5090,0.0483</t>
+  </si>
+  <si>
+    <t>0.0262,0.9166,0.1349,0.0102</t>
+  </si>
+  <si>
+    <t>0.0099,0.9553,0.2034,0.0020</t>
+  </si>
+  <si>
+    <t>0.0084,0.9649,0.1278,0.0013</t>
+  </si>
+  <si>
+    <t>0.0031,0.0160,0.9895,0.0034</t>
+  </si>
+  <si>
+    <t>0.0043,0.0457,0.9846,0.0023</t>
+  </si>
+  <si>
+    <t>0.0436,0.0118,0.9519,0.0073</t>
+  </si>
+  <si>
+    <t>0.0699,0.0154,0.9292,0.0060</t>
+  </si>
+  <si>
+    <t>0.0235,0.0488,0.9338,0.0198</t>
+  </si>
+  <si>
+    <t>0.0084,0.2081,0.9414,0.0026</t>
+  </si>
+  <si>
+    <t>0.9419,0.0666,0.0092,0.0028</t>
+  </si>
+  <si>
+    <t>0.9348,0.0415,0.0120,0.0102</t>
+  </si>
+  <si>
+    <t>0.8933,0.1395,0.0158,0.0030</t>
+  </si>
+  <si>
+    <t>0.0077,0.0170,0.9856,0.0030</t>
+  </si>
+  <si>
+    <t>0.9743,0.0216,0.0042,0.0020</t>
+  </si>
+  <si>
+    <t>0.9665,0.0262,0.0038,0.0043</t>
+  </si>
+  <si>
+    <t>0.9597,0.0454,0.0057,0.0024</t>
+  </si>
+  <si>
+    <t>0.0028,0.4757,0.9421,0.0027</t>
+  </si>
+  <si>
+    <t>0.0025,0.0800,0.9830,0.0038</t>
+  </si>
+  <si>
+    <t>0.0101,0.0411,0.9629,0.0131</t>
+  </si>
+  <si>
+    <t>0.0024,0.4506,0.9595,0.0017</t>
+  </si>
+  <si>
+    <t>0.0026,0.0071,0.9926,0.0017</t>
+  </si>
+  <si>
+    <t>0.0695,0.6243,0.5411,0.0109</t>
+  </si>
+  <si>
+    <t>0.0119,0.9745,0.0798,0.0012</t>
+  </si>
+  <si>
+    <t>0.3564,0.0801,0.6483,0.0188</t>
+  </si>
+  <si>
+    <t>0.6774,0.2081,0.1496,0.0391</t>
+  </si>
+  <si>
+    <t>0.0262,0.2903,0.8843,0.0128</t>
+  </si>
+  <si>
+    <t>0.0032,0.7156,0.8866,0.0020</t>
+  </si>
+  <si>
+    <t>0.0113,0.6265,0.8616,0.0064</t>
+  </si>
+  <si>
+    <t>0.0032,0.9169,0.7218,0.0017</t>
+  </si>
+  <si>
+    <t>0.0074,0.7244,0.8410,0.0047</t>
+  </si>
+  <si>
+    <t>0.2603,0.0278,0.4628,0.2771</t>
+  </si>
+  <si>
+    <t>0.0057,0.0091,0.0056,0.9944</t>
+  </si>
+  <si>
+    <t>0.0015,0.0068,0.0020,0.9983</t>
+  </si>
+  <si>
+    <t>0.0270,0.0199,0.0301,0.9703</t>
+  </si>
+  <si>
+    <t>0.0110,0.0077,0.0393,0.9802</t>
+  </si>
+  <si>
+    <t>0.0129,0.0210,0.0299,0.9804</t>
+  </si>
+  <si>
+    <t>0.0068,0.8472,0.7382,0.0033</t>
+  </si>
+  <si>
+    <t>0.0030,0.4389,0.9506,0.0026</t>
+  </si>
+  <si>
+    <t>0.0109,0.1606,0.9411,0.0094</t>
+  </si>
+  <si>
+    <t>0.0069,0.2427,0.9477,0.0028</t>
+  </si>
+  <si>
+    <t>0.0043,0.4878,0.9359,0.0030</t>
+  </si>
+  <si>
+    <t>0.0335,0.5064,0.7451,0.0168</t>
+  </si>
+  <si>
+    <t>0.9723,0.0210,0.0075,0.0020</t>
+  </si>
+  <si>
+    <t>0.9699,0.0349,0.0034,0.0017</t>
+  </si>
+  <si>
+    <t>0.9657,0.0388,0.0075,0.0017</t>
+  </si>
+  <si>
+    <t>0.9816,0.0141,0.0022,0.0020</t>
+  </si>
+  <si>
+    <t>0.9551,0.0273,0.0148,0.0040</t>
+  </si>
+  <si>
+    <t>0.9870,0.0094,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9573,0.0487,0.0096,0.0025</t>
+  </si>
+  <si>
+    <t>0.9568,0.0415,0.0095,0.0026</t>
+  </si>
+  <si>
+    <t>0.9797,0.0147,0.0031,0.0021</t>
+  </si>
+  <si>
+    <t>0.9893,0.0110,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9747,0.0217,0.0046,0.0020</t>
+  </si>
+  <si>
+    <t>0.9811,0.0149,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9805,0.0222,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.9862,0.0149,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9823,0.0134,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.9736,0.0178,0.0041,0.0030</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.9971,0.0015</t>
+  </si>
+  <si>
+    <t>0.0421,0.0618,0.9186,0.0037</t>
+  </si>
+  <si>
+    <t>0.1597,0.0282,0.4410,0.4366</t>
+  </si>
+  <si>
+    <t>0.0597,0.0217,0.9273,0.0071</t>
+  </si>
+  <si>
+    <t>0.2364,0.7109,0.1213,0.0100</t>
+  </si>
+  <si>
+    <t>0.2109,0.8139,0.0499,0.0073</t>
+  </si>
+  <si>
+    <t>0.3645,0.7317,0.0295,0.0060</t>
+  </si>
+  <si>
+    <t>0.5510,0.5144,0.0393,0.0113</t>
+  </si>
+  <si>
+    <t>0.1306,0.8499,0.0943,0.0067</t>
+  </si>
+  <si>
+    <t>0.0356,0.9574,0.0331,0.0013</t>
+  </si>
+  <si>
+    <t>0.3468,0.7550,0.0244,0.0044</t>
+  </si>
+  <si>
+    <t>0.3178,0.1044,0.6349,0.0507</t>
+  </si>
+  <si>
+    <t>0.0966,0.0661,0.8551,0.0088</t>
+  </si>
+  <si>
+    <t>0.2152,0.1127,0.7170,0.0166</t>
+  </si>
+  <si>
+    <t>0.4079,0.2511,0.4117,0.0520</t>
+  </si>
+  <si>
+    <t>0.3647,0.0813,0.6299,0.0462</t>
+  </si>
+  <si>
+    <t>0.0019,0.9894,0.0530,0.0003</t>
+  </si>
+  <si>
+    <t>0.0166,0.9305,0.2621,0.0044</t>
+  </si>
+  <si>
+    <t>0.1662,0.7028,0.2083,0.0352</t>
+  </si>
+  <si>
+    <t>0.0026,0.9719,0.4017,0.0008</t>
+  </si>
+  <si>
+    <t>0.0748,0.8583,0.1962,0.0080</t>
+  </si>
+  <si>
+    <t>0.6316,0.4394,0.0461,0.0051</t>
+  </si>
+  <si>
+    <t>0.5442,0.4856,0.0647,0.0062</t>
+  </si>
+  <si>
+    <t>0.9130,0.0905,0.0170,0.0058</t>
+  </si>
+  <si>
+    <t>0.9632,0.0257,0.0036,0.0068</t>
+  </si>
+  <si>
+    <t>0.9636,0.0258,0.0049,0.0048</t>
+  </si>
+  <si>
+    <t>0.9599,0.0321,0.0054,0.0038</t>
+  </si>
+  <si>
+    <t>0.9749,0.0187,0.0026,0.0032</t>
+  </si>
+  <si>
+    <t>0.8891,0.0711,0.0511,0.0074</t>
+  </si>
+  <si>
+    <t>0.9628,0.0266,0.0068,0.0046</t>
+  </si>
+  <si>
+    <t>0.9509,0.0237,0.0161,0.0079</t>
+  </si>
+  <si>
+    <t>0.0050,0.7087,0.8581,0.0033</t>
+  </si>
+  <si>
+    <t>0.0043,0.1770,0.9714,0.0011</t>
+  </si>
+  <si>
+    <t>0.0106,0.0908,0.9564,0.0061</t>
+  </si>
+  <si>
+    <t>0.0107,0.1928,0.9393,0.0027</t>
+  </si>
+  <si>
+    <t>0.2760,0.1561,0.6118,0.0323</t>
+  </si>
+  <si>
+    <t>0.4722,0.0918,0.5377,0.0543</t>
+  </si>
+  <si>
+    <t>0.0930,0.0164,0.8286,0.0933</t>
+  </si>
+  <si>
+    <t>0.3651,0.0915,0.6063,0.0219</t>
+  </si>
+  <si>
+    <t>0.1540,0.0227,0.0502,0.8537</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0036,0.0143,0.0178,0.9920</t>
+  </si>
+  <si>
+    <t>0.0157,0.0120,0.0391,0.9757</t>
+  </si>
+  <si>
+    <t>0.0030,0.3594,0.9529,0.0022</t>
+  </si>
+  <si>
+    <t>0.9599,0.0220,0.0076,0.0088</t>
+  </si>
+  <si>
+    <t>0.9453,0.0435,0.0081,0.0056</t>
+  </si>
+  <si>
+    <t>0.9099,0.0748,0.0146,0.0100</t>
+  </si>
+  <si>
+    <t>0.8928,0.0951,0.0367,0.0047</t>
+  </si>
+  <si>
+    <t>0.9008,0.0913,0.0298,0.0070</t>
+  </si>
+  <si>
+    <t>0.6312,0.0561,0.3530,0.0554</t>
+  </si>
+  <si>
+    <t>0.8131,0.0930,0.1014,0.0194</t>
+  </si>
+  <si>
+    <t>0.0043,0.0447,0.9847,0.0053</t>
+  </si>
+  <si>
+    <t>0.5374,0.0086,0.1624,0.1710</t>
+  </si>
+  <si>
+    <t>0.8222,0.0394,0.0448,0.1018</t>
+  </si>
+  <si>
+    <t>0.3291,0.4887,0.2374,0.0228</t>
+  </si>
+  <si>
+    <t>0.5160,0.2618,0.2909,0.0342</t>
+  </si>
+  <si>
+    <t>0.3350,0.3081,0.4297,0.0343</t>
+  </si>
+  <si>
+    <t>0.2508,0.2404,0.5506,0.0346</t>
+  </si>
+  <si>
+    <t>0.6182,0.1388,0.3272,0.0230</t>
+  </si>
+  <si>
+    <t>0.4167,0.4538,0.1757,0.0537</t>
+  </si>
+  <si>
+    <t>0.9701,0.0190,0.0050,0.0040</t>
+  </si>
+  <si>
+    <t>0.9602,0.0210,0.0055,0.0077</t>
+  </si>
+  <si>
+    <t>0.9759,0.0180,0.0015,0.0030</t>
+  </si>
+  <si>
+    <t>0.8827,0.0458,0.0718,0.0112</t>
+  </si>
+  <si>
+    <t>0.9812,0.0136,0.0012,0.0025</t>
+  </si>
+  <si>
+    <t>0.9628,0.0344,0.0053,0.0026</t>
+  </si>
+  <si>
+    <t>0.9756,0.0146,0.0021,0.0045</t>
+  </si>
+  <si>
+    <t>0.9806,0.0163,0.0017,0.0021</t>
+  </si>
+  <si>
+    <t>0.2591,0.7991,0.0276,0.0076</t>
+  </si>
+  <si>
+    <t>0.8326,0.1938,0.0292,0.0051</t>
+  </si>
+  <si>
+    <t>0.3076,0.7641,0.0344,0.0035</t>
+  </si>
+  <si>
+    <t>0.1604,0.0613,0.8397,0.0089</t>
+  </si>
+  <si>
+    <t>0.9252,0.1001,0.0065,0.0034</t>
+  </si>
+  <si>
+    <t>0.7263,0.2936,0.0588,0.0151</t>
+  </si>
+  <si>
+    <t>0.8978,0.0635,0.0428,0.0101</t>
+  </si>
+  <si>
+    <t>0.8775,0.1109,0.0359,0.0092</t>
+  </si>
+  <si>
+    <t>0.0048,0.0076,0.9935,0.0019</t>
+  </si>
+  <si>
+    <t>0.9165,0.0667,0.0229,0.0065</t>
+  </si>
+  <si>
+    <t>0.0182,0.0096,0.9712,0.0070</t>
+  </si>
+  <si>
+    <t>0.0080,0.0140,0.9800,0.0080</t>
+  </si>
+  <si>
+    <t>0.0782,0.0088,0.9287,0.0157</t>
+  </si>
+  <si>
+    <t>0.0034,0.0677,0.9819,0.0030</t>
+  </si>
+  <si>
+    <t>0.1313,0.0327,0.8471,0.0161</t>
+  </si>
+  <si>
+    <t>0.0113,0.0035,0.9857,0.0048</t>
+  </si>
+  <si>
+    <t>0.0070,0.0202,0.9836,0.0021</t>
+  </si>
+  <si>
+    <t>0.0844,0.0489,0.8783,0.0099</t>
+  </si>
+  <si>
+    <t>0.3519,0.0427,0.6893,0.0360</t>
+  </si>
+  <si>
+    <t>0.3539,0.0730,0.6479,0.0289</t>
+  </si>
+  <si>
+    <t>0.2853,0.0327,0.7682,0.0151</t>
+  </si>
+  <si>
+    <t>0.1415,0.0670,0.8163,0.0161</t>
+  </si>
+  <si>
+    <t>0.0323,0.0481,0.9413,0.0052</t>
+  </si>
+  <si>
+    <t>0.2572,0.0428,0.7702,0.0331</t>
+  </si>
+  <si>
+    <t>0.4188,0.0859,0.5674,0.0273</t>
+  </si>
+  <si>
+    <t>0.8320,0.2383,0.0161,0.0049</t>
+  </si>
+  <si>
+    <t>0.9159,0.1244,0.0084,0.0022</t>
+  </si>
+  <si>
+    <t>0.6567,0.3853,0.0495,0.0086</t>
+  </si>
+  <si>
+    <t>0.9729,0.0223,0.0029,0.0027</t>
+  </si>
+  <si>
+    <t>0.9492,0.0587,0.0088,0.0030</t>
+  </si>
+  <si>
+    <t>0.2467,0.0320,0.7950,0.0209</t>
+  </si>
+  <si>
+    <t>0.2297,0.0371,0.7798,0.0428</t>
+  </si>
+  <si>
+    <t>0.3213,0.1192,0.3761,0.3420</t>
+  </si>
+  <si>
+    <t>0.1604,0.0223,0.7781,0.0936</t>
+  </si>
+  <si>
+    <t>0.3846,0.0917,0.5979,0.0666</t>
+  </si>
+  <si>
+    <t>0.1154,0.0270,0.6065,0.3340</t>
+  </si>
+  <si>
+    <t>0.0347,0.0369,0.9377,0.0143</t>
+  </si>
+  <si>
+    <t>0.0404,0.0336,0.9273,0.0179</t>
+  </si>
+  <si>
+    <t>0.0326,0.0247,0.9500,0.0167</t>
+  </si>
+  <si>
+    <t>0.0174,0.0322,0.9556,0.0156</t>
+  </si>
+  <si>
+    <t>0.9813,0.0117,0.0030,0.0024</t>
+  </si>
+  <si>
+    <t>0.9770,0.0150,0.0028,0.0031</t>
+  </si>
+  <si>
+    <t>0.9690,0.0332,0.0036,0.0020</t>
+  </si>
+  <si>
+    <t>0.9702,0.0292,0.0025,0.0028</t>
+  </si>
+  <si>
+    <t>0.9765,0.0181,0.0028,0.0030</t>
+  </si>
+  <si>
+    <t>0.9657,0.0441,0.0042,0.0015</t>
+  </si>
+  <si>
+    <t>0.9688,0.0237,0.0032,0.0040</t>
+  </si>
+  <si>
+    <t>0.9658,0.0301,0.0076,0.0025</t>
+  </si>
+  <si>
+    <t>0.2865,0.0620,0.7378,0.0263</t>
+  </si>
+  <si>
+    <t>0.2126,0.3428,0.5074,0.0120</t>
+  </si>
+  <si>
+    <t>0.7810,0.1377,0.0394,0.0513</t>
+  </si>
+  <si>
+    <t>0.0129,0.0771,0.9558,0.0036</t>
+  </si>
+  <si>
+    <t>0.0024,0.0036,0.9919,0.0054</t>
+  </si>
+  <si>
+    <t>0.0392,0.0221,0.9433,0.0114</t>
+  </si>
+  <si>
+    <t>0.0021,0.0036,0.9917,0.0053</t>
+  </si>
+  <si>
+    <t>0.0211,0.0416,0.9542,0.0031</t>
+  </si>
+  <si>
+    <t>0.0008,0.0070,0.9942,0.0037</t>
+  </si>
+  <si>
+    <t>0.0146,0.0198,0.9649,0.0110</t>
+  </si>
+  <si>
+    <t>0.1433,0.1255,0.7651,0.0131</t>
+  </si>
+  <si>
+    <t>0.2452,0.0567,0.7412,0.0311</t>
+  </si>
+  <si>
+    <t>0.2359,0.0265,0.7964,0.0213</t>
+  </si>
+  <si>
+    <t>0.4308,0.0569,0.5794,0.0494</t>
+  </si>
+  <si>
+    <t>0.9433,0.0509,0.0093,0.0048</t>
+  </si>
+  <si>
+    <t>0.9809,0.0159,0.0026,0.0018</t>
+  </si>
+  <si>
+    <t>0.9696,0.0329,0.0034,0.0016</t>
+  </si>
+  <si>
+    <t>0.9386,0.0493,0.0114,0.0062</t>
+  </si>
+  <si>
+    <t>0.9669,0.0306,0.0023,0.0040</t>
+  </si>
+  <si>
+    <t>0.9598,0.0351,0.0065,0.0035</t>
+  </si>
+  <si>
+    <t>0.9807,0.0168,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.9860,0.0099,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.0072,0.0139,0.9847,0.0021</t>
+  </si>
+  <si>
+    <t>0.0047,0.0719,0.9778,0.0031</t>
+  </si>
+  <si>
+    <t>0.0099,0.0092,0.9828,0.0048</t>
+  </si>
+  <si>
+    <t>0.0565,0.0760,0.8888,0.0083</t>
+  </si>
+  <si>
+    <t>0.0027,0.0025,0.9938,0.0027</t>
+  </si>
+  <si>
+    <t>0.1093,0.0197,0.8458,0.0717</t>
+  </si>
+  <si>
+    <t>0.1423,0.0517,0.8041,0.0195</t>
+  </si>
+  <si>
+    <t>0.0381,0.0206,0.8915,0.1159</t>
+  </si>
+  <si>
+    <t>0.0537,0.0185,0.0122,0.9656</t>
+  </si>
+  <si>
+    <t>0.0123,0.0162,0.0101,0.9887</t>
+  </si>
+  <si>
+    <t>0.0454,0.0265,0.0287,0.9589</t>
+  </si>
+  <si>
+    <t>0.0007,0.0028,0.0009,0.9992</t>
+  </si>
+  <si>
+    <t>0.0014,0.0038,0.0007,0.9989</t>
+  </si>
+  <si>
+    <t>0.5071,0.1964,0.3649,0.1224</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2606,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2858,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2886,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2956,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3012,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3670,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>261</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4230,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
